--- a/www/terminologies/ASS-A15-SexeProvenanceISO-Sexe.xlsx
+++ b/www/terminologies/ASS-A15-SexeProvenanceISO-Sexe.xlsx
@@ -99,13 +99,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R267-SexeProvenanceISO/FHIR/TRE-R267-SexeProvenanceISO|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R267-SexeProvenanceISO/FHIR/TRE-R267-SexeProvenanceISO</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R249-Sexe/FHIR/TRE-R249-Sexe|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R249-Sexe/FHIR/TRE-R249-Sexe</t>
   </si>
   <si>
     <t>0</t>
